--- a/data/seed/portfolio/L-2025-3462/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3462/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,31 +560,31 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>35580000</v>
+        <v>4427000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2836 01.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №109/26 от 01.07.2026</t>
         </is>
       </c>
     </row>
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>4536000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>7163000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shartnoma №188/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №4982</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>3484000</v>
+        <v>12778000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Angren Non MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>217911852</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000879512528001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3446</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3366 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>2518000</v>
+        <v>4895000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №279/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +722,35 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>2665000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>8332000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>258901422</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4607</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №484</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -764,39 +759,39 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3504000</v>
+        <v>17326000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Bunyodkor Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>382491107</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000257122405001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9696</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №181/26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -804,40 +799,40 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>15459000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>5628000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chust Moy MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>234420858</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000263229161001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2172 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №285/26 от 08.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -847,21 +842,21 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>12464000</v>
+        <v>12746000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Guliston Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>285735337</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000376526877001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -871,14 +866,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetazilgan tovar uchun to'lov h/f №1799</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7679 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -886,40 +881,40 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>7939000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>1194000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>268440314</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000399118812001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9393</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,40 +922,40 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>1597000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>3861000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №107/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №184/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,34 +964,39 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8332000</v>
+        <v>3525000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Xiva Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Оплата за упаковочные материалы, с/ф №9652</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,23 +1004,23 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>35013000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>5187000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №160/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>8206000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>1136000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №263/26, QQS 12%</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,40 +1086,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>1380000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>1136000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №236/26, QQS 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>6666000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>2324000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №37/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №934</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>1194000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>16140000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saodat Qurilish XK</t>
+          <t>Ilhom Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>271202054</t>
+          <t>327419442</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000604646841001</t>
+          <t>20208000635726018001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №96/23</t>
+          <t>Предоплата за товар по договору №165/26 от 17.07.2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1210,39 +1210,39 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19211000</v>
+        <v>1579000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №22/26, QQS BILAN</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №159/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,23 +1250,23 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>2032000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>4170000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>295598840</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000660796863001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7218</t>
+          <t>Предоплата за материалы по договору №134/26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,38 +1293,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>3060000</v>
+        <v>53065000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Oltin Vodiy Agro Servis AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>285531508</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000732827481001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOBFAKTURA №9385 10.07.2026, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №13/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>1765000</v>
+        <v>6585000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Omad Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>239882932</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000237458384001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №275/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>3392000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>2178000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9314 13.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №220/26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1415,39 +1415,39 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>33849000</v>
+        <v>4384000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1392</t>
+          <t>Tovarlar uchun to'lov h/f №7239</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>2297000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>8518000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8291 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №231/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,40 +1496,35 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>1718000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>12900000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>258901422</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>16307000332283918417</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7098 от 1.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1538,39 +1533,39 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1136000</v>
+        <v>16307000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №194/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>1136000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>2019000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Оплата за товар по счет-фактуре №9161 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1621,38 +1616,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>1414000</v>
+        <v>9003000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №13/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №6590 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1661,39 +1656,39 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>11979000</v>
+        <v>2331000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №173/26</t>
+          <t>Оплата за товары согласно с/ф №1034</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>7944000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>2336000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8660 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №201/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,40 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>5606000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>746000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000253848223001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №912</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1783,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>1931000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>1964000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1825,34 +1820,39 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>12900000</v>
+        <v>2701000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
+          <t>Xiva Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>16307000332283918417</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товары согласно с/ф №9418</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1862,38 +1862,38 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>9064000</v>
+        <v>18537000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1304</t>
+          <t>Оплата за продукцию по договору №99/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>7579000</v>
+        <v>9656000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Shodlik Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>368860458</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000007683306001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7779 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,40 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>2308000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>2448000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>346204903</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000929579155001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №75/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №239/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>1601000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>2813000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4694</t>
+          <t>Materiallr uchun oldindan to'lov, shartnoma №3/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2025,39 +2025,39 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1750000</v>
+        <v>3341000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>346204903</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000929579155001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №39/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №5390</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2066,39 +2066,39 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1991000</v>
+        <v>38764000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Оплата за упаковочные материалы, с/ф №8054</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>3943000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>2468000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guliston Dori-Darmon MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>291855315</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000827328274001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2475</t>
+          <t>Оплата за товар по счет-фактуре №8476 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>746000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>2318000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oltin Vodiy Agro Servis AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>285531508</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000998697504001</t>
+          <t>20208000732827481001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Предоплата за товар по договору №117/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2428000</v>
+        <v>1921000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2214,14 +2214,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5197</t>
+          <t>Оплата за упаковочные материалы, с/ф №4156</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2230,22 +2230,17 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1162000</v>
+        <v>300000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>262398829</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2255,14 +2250,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №275/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2271,39 +2266,39 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1512000</v>
+        <v>1713000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5085</t>
+          <t>Предоплата за материалы по договору №271/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2306,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>5511000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>6091000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Xomashyo uchun to'lov, shartnoma №18/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №75/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2349,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>4754000</v>
+        <v>5577000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angren Non MChJ</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>217911852</t>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000879512528001</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1582</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7806</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2390,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>1326000</v>
+        <v>1303000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3850</t>
+          <t>Предоплата за товар по договору №286/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,40 +2429,40 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>1265000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>1077000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №21/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №9797 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2476,39 +2471,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1278000</v>
+        <v>2054000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Guliston Dori-Darmon MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>291855315</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000827328274001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №244/26</t>
+          <t>Оплата за сырье по договору №13/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2517,22 +2512,22 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>3778000</v>
+        <v>4118000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,14 +2537,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №84/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №108/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,23 +2552,23 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>8491000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>9713000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2583,14 +2578,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №293/26</t>
+          <t>Оплата за товар по с/ф №6914 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2593,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>7224000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>2461000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2865</t>
+          <t>Оплата за транспортные услуги по договору №109/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2640,7 +2635,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>300000</v>
+        <v>8566000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
@@ -2660,14 +2655,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2675,23 +2670,23 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>3194000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>2168000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2701,14 +2696,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9214</t>
+          <t>Оплата за товар по счет-фактуре №2801 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2718,38 +2713,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>22979000</v>
+        <v>22298000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7984</t>
+          <t>Оплата за продукцию по дог. №247/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2759,21 +2754,21 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2808000</v>
+        <v>11453000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Ilhom Savdo MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>327419442</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000635726018001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2783,14 +2778,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8834 05.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6152 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2798,40 +2793,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>5005000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>4656000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №207/26, QQS BILAN</t>
+          <t>Оплата по счет-фактуре №8330 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2839,40 +2834,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>5445000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>1864000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №299/26</t>
+          <t>Shartnoma №269/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2880,35 +2875,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>8566000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>1315000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Chirchiq Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №9833</t>
+          <t>Оплата по счет-фактуре №3128 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2916,40 +2916,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>11340000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>1228000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>268440314</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000399118812001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №217/26, QQS 12%</t>
+          <t>Аренда помещения за август, дог. №75/24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2957,40 +2957,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>1228000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>3933000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saodat Qurilish XK</t>
+          <t>Ilhom Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>271202054</t>
+          <t>327419442</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000604646841001</t>
+          <t>20208000635726018001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №96/23</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,38 +3000,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>4099000</v>
+        <v>2146000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3578</t>
+          <t>Предоплата за товар по договору №12/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3040,39 +3040,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>3674000</v>
+        <v>4279000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №34/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №24/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3081,39 +3081,39 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>28204000</v>
+        <v>8796000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №68/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1054</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3123,38 +3123,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>4458000</v>
+        <v>10119000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1738 11.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №121/26 от 12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,23 +3162,23 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>4923000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>2799000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №297</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №250/26 ОТ 12.08.2026</t>
         </is>
       </c>
     </row>
@@ -3203,40 +3203,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>9293000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>2149000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №185/26 от 13.08.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №94/26 от 13.08.2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3245,32 +3245,32 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1168000</v>
+        <v>5249000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №9459</t>
         </is>
       </c>
     </row>
@@ -3285,33 +3285,33 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>1168000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>1598000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №7554 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3328,31 +3328,31 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>10945000</v>
+        <v>2153000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №159/26 ОТ 17.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №7558 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3369,31 +3369,31 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>7196000</v>
+        <v>2092000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №236 17.08.2026, QQS BILAN</t>
+          <t>Оплата по счет-фактуре №28 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3410,21 +3410,21 @@
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>3619000</v>
+        <v>2058000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Ilhom Savdo MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>327419442</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000635726018001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1460</t>
+          <t>Mahsulot uchun to'lov, shartnoma №17/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -3451,31 +3451,31 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>2906000</v>
+        <v>1966000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №87/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №105/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3490,23 +3490,23 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>12221000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>1226000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9023</t>
+          <t>Оплата за продукцию по дог. №12/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3532,39 +3532,39 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>25307000</v>
+        <v>1168000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №131/26</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3573,39 +3573,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>2851000</v>
+        <v>1168000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №10/26</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3613,40 +3613,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>21118000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>9467000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Bunyodkor Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>382491107</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000257122405001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9489</t>
+          <t>Оплата за сырье по договору №115/26 от 18.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3656,38 +3656,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>12196000</v>
+        <v>7894000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SHARTNOMA №56/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Mahsulot uchun to'lov, shartn. №130/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,33 +3695,33 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>5996000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>3343000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8403 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №190/26</t>
         </is>
       </c>
     </row>
@@ -3736,35 +3736,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>12900000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>3788000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
+          <t>Chirchiq Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16307000332283918417</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №503 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3772,40 +3777,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>3061000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Предоплата за товар по дог. №291/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,23 +3818,18 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>17309000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>12900000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>206604930</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>16307000332283918417</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3839,14 +3839,14 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3191 24.08.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3856,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>1740000</v>
+        <v>2724000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №201/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №3691 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>12062000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>1957000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата посчет-фактуре №2620 за поставленный товар</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>2252000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>2631000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5900</t>
+          <t>Оплата за сырье по договору №97/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,38 +3979,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>4350000</v>
+        <v>11233000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №162/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №1497 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4019,39 +4019,39 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>10576000</v>
+        <v>2066000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Xom ashyo ucun to'lov, shartnoma №135/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №889</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>7050000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>5014000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №978 27.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №6497</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>2383000</v>
+        <v>4539000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №122/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №6475 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,22 +4142,22 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>767000</v>
+        <v>5234000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>346204903</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000998697504001</t>
+          <t>20208000929579155001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4167,14 +4167,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Elekr energiyasi uchun to'lov</t>
+          <t>Предоплата за материалы по договору №297/26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4183,39 +4183,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>4594000</v>
+        <v>767000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000253848223001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №13/26</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>11831000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>2431000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9077 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №76/26 от 26.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4264,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>6031000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>2684000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Bunyodkor Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>382491107</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000257122405001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6951 31.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9836</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4306,34 +4306,39 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>300000</v>
+        <v>11783000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Farg'ona Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>260422520</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000942784837001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за сырье по договору №125/26 от 26.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4341,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>38033000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>3254000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Shodlik Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>368860458</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000007683306001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №101/26</t>
+          <t>Оплата за продукцию по договору №150/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4382,40 +4387,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>1067000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>7019000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>346204903</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000929579155001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2109 01.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №271/26 от 27.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4425,21 +4430,21 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>2922000</v>
+        <v>7389000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Ilhom Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>327419442</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000635726018001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4449,14 +4454,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1124 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2441 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4464,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>5568000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>6366000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Shodlik Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>368860458</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000007683306001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №152/26</t>
+          <t>Оплата за продукцию по договору №48/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,35 +4510,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>9065000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>3656000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Chirchiq Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по дог. №60/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4541,23 +4551,23 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>52374000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>2732000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4567,14 +4577,14 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №165/26</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4584,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>3771000</v>
+        <v>2045000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6726</t>
+          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4625,38 +4635,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>3579000</v>
+        <v>1755000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8466</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5078</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4666,38 +4676,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>2685000</v>
+        <v>1602000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Shodlik Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>368860458</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000007683306001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2926 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №293/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4707,38 +4717,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>1151000</v>
+        <v>1304000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Oltin Vodiy Agro Servis AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>285531508</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000732827481001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, sharn. №74/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №166/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4747,22 +4757,17 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>1182000</v>
+        <v>300000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>262398829</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4772,14 +4777,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5282</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4788,39 +4793,39 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>6864000</v>
+        <v>6391000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>346204903</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000929579155001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №107/26</t>
+          <t>Оплата за сырье по договору №78/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4828,40 +4833,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>3127000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>56505000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Shartnoma №84/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата затранспортные услуги по договору №155/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4871,38 +4876,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1071000</v>
+        <v>2451000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Shartnoma №226/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4911,22 +4916,22 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1299000</v>
+        <v>36910000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Saodat Qurilish XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>271202054</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000604646841001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4936,14 +4941,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №96/23</t>
+          <t>Оплата за транспортные услуги по договору №122/26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4951,23 +4956,23 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>14085000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>17057000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4977,14 +4982,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №103/26</t>
+          <t>Оплата по счет-фактуре №2312 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4994,38 +4999,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>3554000</v>
+        <v>3794000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9588 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5035,38 +5040,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>84650000</v>
+        <v>2248000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7215</t>
+          <t>Предоплата за товар по дог. №33/26 от 03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5074,40 +5079,35 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>4033000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>9065000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>258901422</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7692</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5117,38 +5117,38 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>1964000</v>
+        <v>9106000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Shodlik Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>368860458</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000007683306001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2548</t>
+          <t>Оплата за продукцию по дог. №182/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5156,40 +5156,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>1765000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>9342000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>295598840</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000660796863001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №282/26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5197,40 +5197,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>1300000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>18782000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №156/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №162/26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5238,40 +5238,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>1236000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>2906000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Shartnoma №249/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,39 +5280,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>1236000</v>
+        <v>1299000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>268440314</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000399118812001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Аренда помещения за сентябрь, дог. №75/24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,40 +5320,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>5459000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>3365000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №154/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3101 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5362,39 +5362,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>37884000</v>
+        <v>5437000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №273/26</t>
+          <t>Оплата за сырье по договору №122/26 от 11.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,40 +5402,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>2268000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>12924000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Farg'ona Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>260422520</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000942784837001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6070</t>
+          <t>Оплата за сырье по дог. №170/26 от 11.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5443,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>1210000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>1913000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guliston Dori-Darmon MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>291855315</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000827328274001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №93/26</t>
+          <t>Tovar uchun to'lov, h/f №2794 14.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5484,40 +5484,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>2542000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>1613000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7764</t>
+          <t>Оплата по счет-фактуре №1712 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5526,39 +5526,39 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>2703000</v>
+        <v>4541000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9219</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №253/26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5566,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>3396000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>8426000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Bunyodkor Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>382491107</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000257122405001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9590</t>
+          <t>Xom ashyo uchun to'lov, shartn. №18/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5609,38 +5609,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>1998000</v>
+        <v>3312000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8701 18.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №256/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,35 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>12900000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>1781000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
+          <t>Saodat Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>391185238</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>16307000332283918417</t>
+          <t>20208000951252846001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за товар по договору №160/26 от 15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5684,40 +5689,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>6724000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>1236000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7775</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,40 +5730,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>2405000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>1236000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9689 21.09.2026, QQS bilan</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5768,38 +5773,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>1476000</v>
+        <v>9745000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №292/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №4493 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5814,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>1188000</v>
+        <v>2895000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Oltin Vodiy Agro Servis AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>285531508</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000732827481001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №190/26 от 21.09.2026</t>
+          <t>Предоплата за товар по договору №246/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5848,40 +5853,40 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>981000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>1393000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №193/26</t>
+          <t>Предоплата за товар по дог. №15/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5890,39 +5895,39 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1086000</v>
+        <v>3850000</v>
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Guliston Dori-Darmon MChJ</t>
+          <t>Qo'qon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>291855315</t>
+          <t>292008292</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000827328274001</t>
+          <t>20208000566278827001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6560</t>
+          <t>Оплата за сырье по договору №93/26 от 17.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>1135000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>8147000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Durdona Agro MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>255180597</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000036534543001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №134/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №6126 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5972,39 +5977,39 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1615000</v>
+        <v>6247000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>390857353</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №248/26, QQS bilan</t>
+          <t>Оплата за сырье по дог. №294/26 от 18.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6013,22 +6018,17 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>1642000</v>
+        <v>12900000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>390857353</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3462)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>16307000332283918417</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6038,14 +6038,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-3462 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6055,38 +6055,38 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>6547000</v>
+        <v>21021000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №13/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6096,38 +6096,38 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>4303000</v>
+        <v>2165000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5189 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4075 21.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6137,38 +6137,38 @@
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>2183000</v>
+        <v>2083000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №10/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №237/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6177,32 +6177,32 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1256000</v>
+        <v>21911000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>225810262</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>20208000931160550001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №104/26</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №2573</t>
         </is>
       </c>
     </row>
@@ -6217,40 +6217,40 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>2206000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>15322000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3570 22.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6259,32 +6259,32 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>3598000</v>
+        <v>2062000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>262398829</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000292374583001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №74/26</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
     </row>
@@ -6300,32 +6300,32 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>6530000</v>
+        <v>812000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000253848223001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №205/26, QQS bilan</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
@@ -6342,31 +6342,31 @@
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>4947000</v>
+        <v>6305000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1569</t>
+          <t>Shartnoma №129/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -6383,31 +6383,31 @@
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>2668000</v>
+        <v>2735000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №295/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №103/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -6422,33 +6422,33 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>1689000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>5325000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Farg'ona Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>260422520</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000942784837001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №40/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №48/26</t>
         </is>
       </c>
     </row>
@@ -6465,31 +6465,31 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>2612000</v>
+        <v>2876000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2667 25.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №7220 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -6506,38 +6506,38 @@
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>2099000</v>
+        <v>1595000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bunyodkor Meva Eksport MChJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>218274194</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000296357260001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Shartnoma №272/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №700 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6547,38 +6547,38 @@
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>2073000</v>
+        <v>26366000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Oqtosh Savdo MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>360493044</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000442547251001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1680 25.09.2026, QQS bilan</t>
+          <t>Оплата по с/ф №8279 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6588,38 +6588,38 @@
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>1187000</v>
+        <v>5369000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Farg'ona Metall MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>341551805</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000770365345001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2812</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6627,40 +6627,40 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>812000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>5201000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000998697504001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Оплата по счет-фактуре №3467 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6668,23 +6668,23 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>3354000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>4262000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sharq Moy AJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>234105253</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000723948994001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №115/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №4899 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -6711,31 +6711,31 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>5828000</v>
+        <v>3161000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ilhom Farm Savdo MChJ</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>206604930</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000434425472001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Yetkazilan tovar uchun to'lov h/f №5718</t>
+          <t>Предоплата за товар по договору №237/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
@@ -6752,31 +6752,31 @@
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>4342000</v>
+        <v>1608000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chirchiq Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>390142297</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000583615974001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2257 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №192/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
@@ -6791,40 +6791,40 @@
           <t>253</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>2751000</v>
-      </c>
+      <c r="C163" s="2" t="n">
+        <v>3816000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Chust Moy MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>234420858</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000263229161001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №781 28.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №115/26</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6833,22 +6833,17 @@
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>1282000</v>
+        <v>300000</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Zarafshon Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>390857353</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000733765268001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6858,14 +6853,14 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №69/26</t>
+          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6873,177 +6868,59 @@
           <t>255</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>2402000</v>
-      </c>
+      <c r="C165" s="2" t="n">
+        <v>8798000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy XK</t>
+          <t>Nihol Polimer AJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>258901422</t>
+          <t>289728678</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000725836159001</t>
+          <t>20208000625887151001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №248/26</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>2856000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Yulduz Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>262398829</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000292374583001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №44/26, QQS bilan</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>503976000</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>498576000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>2074000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Marg'ilon Moy XK</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>258901422</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000725836159001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4939 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Zarafshon Kredit Bank</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="n">
-        <v>529779000</v>
-      </c>
-      <c r="D169" s="4" t="n">
-        <v>524379000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C170" s="4" t="n">
+      <c r="C167" s="4" t="n">
         <v>28600000</v>
       </c>
-      <c r="D170" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
